--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="509">
   <si>
     <t>Filename</t>
   </si>
@@ -808,730 +808,739 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9935,0.0040,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.8703,0.0002,0.0000,0.1718</t>
-  </si>
-  <si>
-    <t>0.9943,0.0015,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.8387,0.0007,0.0001,0.1744</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9871,0.0060,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.8225,0.0003,0.0000,0.2481</t>
+  </si>
+  <si>
+    <t>0.9884,0.0042,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9283,0.0023,0.0006,0.0409</t>
+  </si>
+  <si>
+    <t>0.9991,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0013,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9992,0.0008,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0000,0.0000</t>
+    <t>0.8049,0.1409,0.0453,0.0071</t>
+  </si>
+  <si>
+    <t>0.5529,0.0194,0.4547,0.0100</t>
+  </si>
+  <si>
+    <t>0.5845,0.0131,0.4522,0.0056</t>
+  </si>
+  <si>
+    <t>0.5013,0.2272,0.1683,0.0285</t>
+  </si>
+  <si>
+    <t>0.8158,0.0317,0.1338,0.0132</t>
+  </si>
+  <si>
+    <t>0.0244,0.9719,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.1837,0.8294,0.0258,0.0039</t>
+  </si>
+  <si>
+    <t>0.9854,0.0226,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0363,0.9631,0.0053,0.0007</t>
+  </si>
+  <si>
+    <t>0.0098,0.9857,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.8466,0.0209,0.1171,0.0094</t>
+  </si>
+  <si>
+    <t>0.6283,0.0339,0.2817,0.0522</t>
+  </si>
+  <si>
+    <t>0.1238,0.0025,0.8866,0.0054</t>
+  </si>
+  <si>
+    <t>0.3897,0.0118,0.6237,0.0102</t>
+  </si>
+  <si>
+    <t>0.0887,0.0027,0.9090,0.0087</t>
+  </si>
+  <si>
+    <t>0.0561,0.0017,0.9444,0.0038</t>
+  </si>
+  <si>
+    <t>0.0053,0.0006,0.9847,0.0156</t>
+  </si>
+  <si>
+    <t>0.6869,0.3836,0.0094,0.0018</t>
+  </si>
+  <si>
+    <t>0.9517,0.0295,0.0036,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9973,0.1029</t>
+  </si>
+  <si>
+    <t>0.2183,0.4642,0.3302,0.0149</t>
+  </si>
+  <si>
+    <t>0.9742,0.0228,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.1084,0.0185,0.8761,0.0247</t>
+  </si>
+  <si>
+    <t>0.9747,0.0314,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.2919,0.7326,0.0207,0.0052</t>
+  </si>
+  <si>
+    <t>0.0096,0.8402,0.2484,0.0358</t>
+  </si>
+  <si>
+    <t>0.0068,0.5312,0.2232,0.3597</t>
+  </si>
+  <si>
+    <t>0.1225,0.1651,0.7242,0.0267</t>
+  </si>
+  <si>
+    <t>0.1380,0.0047,0.8708,0.0057</t>
+  </si>
+  <si>
+    <t>0.0645,0.2414,0.7451,0.0170</t>
+  </si>
+  <si>
+    <t>0.0046,0.9799,0.0241,0.0020</t>
+  </si>
+  <si>
+    <t>0.0042,0.0006,0.9908,0.0048</t>
+  </si>
+  <si>
+    <t>0.3921,0.0626,0.0030,0.4379</t>
+  </si>
+  <si>
+    <t>0.0030,0.9943,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9944,0.0008,0.0043</t>
+  </si>
+  <si>
+    <t>0.0005,0.9976,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.0031,0.9608,0.1557</t>
+  </si>
+  <si>
+    <t>0.0151,0.0295,0.9578,0.0134</t>
+  </si>
+  <si>
+    <t>0.0610,0.0013,0.9224,0.0120</t>
+  </si>
+  <si>
+    <t>0.0729,0.0013,0.9335,0.0035</t>
+  </si>
+  <si>
+    <t>0.0031,0.0022,0.9933,0.0036</t>
+  </si>
+  <si>
+    <t>0.0280,0.0052,0.9586,0.0093</t>
+  </si>
+  <si>
+    <t>0.9971,0.0029,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0031,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0004,0.8712,0.4292</t>
+  </si>
+  <si>
+    <t>0.9980,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0034,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9406,0.3446,0.0056</t>
+  </si>
+  <si>
+    <t>0.0008,0.0016,0.9942,0.0117</t>
+  </si>
+  <si>
+    <t>0.0019,0.0005,0.9864,0.0356</t>
+  </si>
+  <si>
+    <t>0.0009,0.9542,0.7095,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0015,0.9957,0.0038</t>
+  </si>
+  <si>
+    <t>0.0713,0.9248,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.0022,0.9971,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9771,0.0153,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.7810,0.0743,0.1432,0.0079</t>
+  </si>
+  <si>
+    <t>0.0029,0.0033,0.9886,0.0284</t>
+  </si>
+  <si>
+    <t>0.0006,0.9703,0.5484,0.0006</t>
+  </si>
+  <si>
+    <t>0.0041,0.9682,0.1693,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.9954,0.0297,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9659,0.5290,0.0008</t>
+  </si>
+  <si>
+    <t>0.0206,0.0004,0.0001,0.9931</t>
+  </si>
+  <si>
+    <t>0.0702,0.0001,0.0000,0.9829</t>
+  </si>
+  <si>
+    <t>0.0438,0.0001,0.0000,0.9906</t>
+  </si>
+  <si>
+    <t>0.4113,0.0012,0.0007,0.7346</t>
+  </si>
+  <si>
+    <t>0.1292,0.0004,0.0001,0.9566</t>
+  </si>
+  <si>
+    <t>0.0269,0.0002,0.0000,0.9930</t>
+  </si>
+  <si>
+    <t>0.0014,0.9450,0.5465,0.0017</t>
+  </si>
+  <si>
+    <t>0.0024,0.9234,0.7099,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.9465,0.5104,0.0015</t>
+  </si>
+  <si>
+    <t>0.0211,0.7181,0.5806,0.0098</t>
+  </si>
+  <si>
+    <t>0.0012,0.9186,0.7713,0.0007</t>
+  </si>
+  <si>
+    <t>0.0098,0.9391,0.1010,0.0166</t>
+  </si>
+  <si>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0029,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0031,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9959,0.0124</t>
+  </si>
+  <si>
+    <t>0.1947,0.0074,0.8282,0.0045</t>
+  </si>
+  <si>
+    <t>0.9217,0.0439,0.0136,0.0037</t>
+  </si>
+  <si>
+    <t>0.1617,0.0027,0.8480,0.0067</t>
+  </si>
+  <si>
+    <t>0.2326,0.8342,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.2237,0.8280,0.0081,0.0005</t>
+  </si>
+  <si>
+    <t>0.8031,0.2761,0.0067,0.0011</t>
+  </si>
+  <si>
+    <t>0.8707,0.1641,0.0078,0.0012</t>
+  </si>
+  <si>
+    <t>0.1008,0.9146,0.0076,0.0006</t>
+  </si>
+  <si>
+    <t>0.0418,0.9655,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9780,0.0342,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.7743,0.0292,0.1921,0.0081</t>
+  </si>
+  <si>
+    <t>0.2345,0.0022,0.7126,0.0211</t>
+  </si>
+  <si>
+    <t>0.9276,0.0463,0.0160,0.0021</t>
+  </si>
+  <si>
+    <t>0.9057,0.0347,0.0384,0.0035</t>
+  </si>
+  <si>
+    <t>0.1953,0.0213,0.0023,0.8378</t>
+  </si>
+  <si>
+    <t>0.0010,0.9961,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1031,0.8794,0.0094,0.0126</t>
+  </si>
+  <si>
+    <t>0.0003,0.9865,0.5654,0.0003</t>
+  </si>
+  <si>
+    <t>0.1788,0.8396,0.0232,0.0011</t>
+  </si>
+  <si>
+    <t>0.9761,0.0287,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9895,0.0108,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0032,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0047,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0069,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0048,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.8404,0.2586,0.0493</t>
+  </si>
+  <si>
+    <t>0.0111,0.6228,0.7841,0.0038</t>
+  </si>
+  <si>
+    <t>0.0319,0.0173,0.9515,0.0063</t>
+  </si>
+  <si>
+    <t>0.0959,0.0762,0.8120,0.0461</t>
+  </si>
+  <si>
+    <t>0.9593,0.0158,0.0080,0.0033</t>
+  </si>
+  <si>
+    <t>0.9466,0.0213,0.0134,0.0037</t>
+  </si>
+  <si>
+    <t>0.9463,0.0092,0.0287,0.0031</t>
+  </si>
+  <si>
+    <t>0.9328,0.0462,0.0111,0.0014</t>
+  </si>
+  <si>
+    <t>0.2952,0.0006,0.0001,0.8593</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0001,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0071,0.0001,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.0002,0.7363,0.8803,0.0018</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9584,0.0609,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9533,0.0625,0.0035,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9717,0.0038,0.0027,0.0075</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.0736,0.9931</t>
+  </si>
+  <si>
+    <t>0.9921,0.0052,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9941,0.0044,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9522,0.0657,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9825,0.0141,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9900,0.0099,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.4359,0.6120,0.0104,0.0054</t>
+  </si>
+  <si>
+    <t>0.9277,0.0482,0.0199,0.0022</t>
+  </si>
+  <si>
+    <t>0.9611,0.0476,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0023,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9993,0.0006,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8745,0.0842,0.0303,0.0033</t>
-  </si>
-  <si>
-    <t>0.5547,0.0151,0.4091,0.0229</t>
-  </si>
-  <si>
-    <t>0.2876,0.0079,0.7475,0.0048</t>
-  </si>
-  <si>
-    <t>0.1062,0.0056,0.8620,0.0258</t>
-  </si>
-  <si>
-    <t>0.6913,0.1302,0.1300,0.0343</t>
-  </si>
-  <si>
-    <t>0.0263,0.9691,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.1008,0.8990,0.0203,0.0019</t>
-  </si>
-  <si>
-    <t>0.8860,0.1821,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.0636,0.9400,0.0082,0.0018</t>
-  </si>
-  <si>
-    <t>0.0272,0.9677,0.0074,0.0012</t>
-  </si>
-  <si>
-    <t>0.7893,0.0522,0.1193,0.0224</t>
-  </si>
-  <si>
-    <t>0.5624,0.0238,0.1559,0.1574</t>
-  </si>
-  <si>
-    <t>0.0234,0.0043,0.9709,0.0056</t>
-  </si>
-  <si>
-    <t>0.3488,0.0035,0.6871,0.0058</t>
-  </si>
-  <si>
-    <t>0.0934,0.0022,0.9012,0.0083</t>
-  </si>
-  <si>
-    <t>0.1413,0.0042,0.8646,0.0078</t>
-  </si>
-  <si>
-    <t>0.0048,0.0007,0.9880,0.0114</t>
-  </si>
-  <si>
-    <t>0.8482,0.1952,0.0072,0.0016</t>
-  </si>
-  <si>
-    <t>0.9570,0.0222,0.0086,0.0036</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9965,0.0347</t>
-  </si>
-  <si>
-    <t>0.2250,0.5615,0.2350,0.0077</t>
-  </si>
-  <si>
-    <t>0.9870,0.0116,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9365,0.0494,0.0156,0.0023</t>
-  </si>
-  <si>
-    <t>0.9784,0.0280,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.1848,0.8103,0.0384,0.0048</t>
-  </si>
-  <si>
-    <t>0.0040,0.2551,0.9146,0.0092</t>
-  </si>
-  <si>
-    <t>0.0262,0.0817,0.8671,0.0722</t>
-  </si>
-  <si>
-    <t>0.1034,0.1641,0.7407,0.0404</t>
-  </si>
-  <si>
-    <t>0.0985,0.0074,0.8963,0.0076</t>
-  </si>
-  <si>
-    <t>0.1517,0.0116,0.8059,0.0320</t>
-  </si>
-  <si>
-    <t>0.0176,0.9141,0.1731,0.0035</t>
-  </si>
-  <si>
-    <t>0.0056,0.0019,0.9793,0.0207</t>
-  </si>
-  <si>
-    <t>0.1614,0.0587,0.0011,0.8088</t>
-  </si>
-  <si>
-    <t>0.0013,0.9970,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9954,0.0007,0.0077</t>
-  </si>
-  <si>
-    <t>0.0006,0.9977,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.0015,0.0139,0.9698,0.0439</t>
-  </si>
-  <si>
-    <t>0.0037,0.0073,0.9794,0.0180</t>
-  </si>
-  <si>
-    <t>0.0679,0.0012,0.9224,0.0090</t>
-  </si>
-  <si>
-    <t>0.1143,0.0011,0.8897,0.0051</t>
-  </si>
-  <si>
-    <t>0.0019,0.0008,0.9954,0.0034</t>
-  </si>
-  <si>
-    <t>0.0403,0.0017,0.9440,0.0106</t>
-  </si>
-  <si>
-    <t>0.9928,0.0085,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0053,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0029,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.0006,0.9466,0.2373</t>
-  </si>
-  <si>
-    <t>0.9977,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9915,0.0107,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9712,0.2161,0.0039</t>
-  </si>
-  <si>
-    <t>0.0019,0.0012,0.9894,0.0211</t>
-  </si>
-  <si>
-    <t>0.0093,0.0024,0.9710,0.0265</t>
-  </si>
-  <si>
-    <t>0.0008,0.9288,0.8302,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.9932,0.0321</t>
-  </si>
-  <si>
-    <t>0.0115,0.9860,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0087,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9062,0.0293,0.0478,0.0076</t>
-  </si>
-  <si>
-    <t>0.0015,0.0018,0.9941,0.0148</t>
-  </si>
-  <si>
-    <t>0.0006,0.9812,0.3729,0.0004</t>
-  </si>
-  <si>
-    <t>0.0103,0.9011,0.4006,0.0022</t>
-  </si>
-  <si>
-    <t>0.0004,0.9956,0.0219,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.9386,0.4335,0.0022</t>
-  </si>
-  <si>
-    <t>0.0441,0.0005,0.0001,0.9855</t>
-  </si>
-  <si>
-    <t>0.0552,0.0001,0.0000,0.9869</t>
-  </si>
-  <si>
-    <t>0.0388,0.0001,0.0000,0.9919</t>
-  </si>
-  <si>
-    <t>0.3945,0.0011,0.0004,0.7584</t>
-  </si>
-  <si>
-    <t>0.0176,0.0001,0.0000,0.9958</t>
-  </si>
-  <si>
-    <t>0.0382,0.0009,0.0001,0.9879</t>
-  </si>
-  <si>
-    <t>0.0015,0.9686,0.3413,0.0020</t>
-  </si>
-  <si>
-    <t>0.0056,0.8065,0.7440,0.0043</t>
-  </si>
-  <si>
-    <t>0.0037,0.9240,0.3746,0.0057</t>
-  </si>
-  <si>
-    <t>0.0091,0.8837,0.4387,0.0047</t>
-  </si>
-  <si>
-    <t>0.0007,0.8965,0.9183,0.0002</t>
-  </si>
-  <si>
-    <t>0.0189,0.8707,0.2760,0.0073</t>
-  </si>
-  <si>
-    <t>0.9988,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9949,0.0061,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0015,0.0000,0.0000</t>
+    <t>0.9990,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9640,0.0392,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9752,0.0328,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9839,0.0196,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9538,0.0537,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0057,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0019,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0041,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0037,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9980,0.0197</t>
+  </si>
+  <si>
+    <t>0.9978,0.0023,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0032,0.9904,0.0018</t>
+  </si>
+  <si>
+    <t>0.0023,0.0267,0.9575,0.0465</t>
+  </si>
+  <si>
+    <t>0.4333,0.0035,0.6508,0.0034</t>
+  </si>
+  <si>
+    <t>0.0107,0.0246,0.9727,0.0119</t>
+  </si>
+  <si>
+    <t>0.0142,0.0016,0.9815,0.0039</t>
+  </si>
+  <si>
+    <t>0.0097,0.0010,0.9876,0.0025</t>
+  </si>
+  <si>
+    <t>0.0235,0.0029,0.9700,0.0068</t>
+  </si>
+  <si>
+    <t>0.6824,0.0429,0.2773,0.0176</t>
+  </si>
+  <si>
+    <t>0.6517,0.0371,0.3268,0.0150</t>
+  </si>
+  <si>
+    <t>0.6560,0.0393,0.3165,0.0127</t>
+  </si>
+  <si>
+    <t>0.7509,0.2704,0.0155,0.0029</t>
+  </si>
+  <si>
+    <t>0.5149,0.1943,0.2215,0.0168</t>
+  </si>
+  <si>
+    <t>0.9109,0.0394,0.0341,0.0021</t>
+  </si>
+  <si>
+    <t>0.7402,0.0920,0.0871,0.0438</t>
+  </si>
+  <si>
+    <t>0.7346,0.1477,0.0527,0.0282</t>
+  </si>
+  <si>
+    <t>0.9674,0.0553,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9751,0.0391,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9885,0.0157,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0162,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9848,0.0193,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8335,0.1324,0.0215,0.0062</t>
+  </si>
+  <si>
+    <t>0.9517,0.0221,0.0142,0.0012</t>
+  </si>
+  <si>
+    <t>0.9304,0.0128,0.0254,0.0097</t>
+  </si>
+  <si>
+    <t>0.7829,0.0601,0.1300,0.0087</t>
+  </si>
+  <si>
+    <t>0.9251,0.0129,0.0433,0.0064</t>
+  </si>
+  <si>
+    <t>0.0148,0.0013,0.9510,0.0621</t>
+  </si>
+  <si>
+    <t>0.0430,0.0202,0.7229,0.2430</t>
+  </si>
+  <si>
+    <t>0.0603,0.4640,0.6178,0.0145</t>
+  </si>
+  <si>
+    <t>0.0496,0.0411,0.9054,0.0231</t>
+  </si>
+  <si>
+    <t>0.0719,0.1839,0.7191,0.0583</t>
+  </si>
+  <si>
+    <t>0.9985,0.0014,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0077,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0036,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0007,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0003,0.9951,0.0134</t>
-  </si>
-  <si>
-    <t>0.1613,0.0091,0.8529,0.0047</t>
-  </si>
-  <si>
-    <t>0.9145,0.0665,0.0101,0.0025</t>
-  </si>
-  <si>
-    <t>0.0307,0.0047,0.9642,0.0059</t>
-  </si>
-  <si>
-    <t>0.1562,0.8834,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.1678,0.8692,0.0067,0.0004</t>
-  </si>
-  <si>
-    <t>0.8454,0.2338,0.0045,0.0009</t>
-  </si>
-  <si>
-    <t>0.9415,0.0737,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.0602,0.9446,0.0062,0.0004</t>
-  </si>
-  <si>
-    <t>0.0306,0.9714,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9741,0.0352,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.8650,0.0971,0.0257,0.0039</t>
-  </si>
-  <si>
-    <t>0.6185,0.0049,0.4048,0.0088</t>
-  </si>
-  <si>
-    <t>0.9213,0.0662,0.0117,0.0019</t>
-  </si>
-  <si>
-    <t>0.9151,0.0493,0.0205,0.0026</t>
-  </si>
-  <si>
-    <t>0.0825,0.0221,0.0009,0.9433</t>
-  </si>
-  <si>
-    <t>0.0006,0.9982,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9971,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.2291,0.8038,0.0115,0.0027</t>
-  </si>
-  <si>
-    <t>0.0001,0.9938,0.4414,0.0001</t>
-  </si>
-  <si>
-    <t>0.3183,0.7298,0.0178,0.0011</t>
-  </si>
-  <si>
-    <t>0.9404,0.0801,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.9891,0.0117,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0037,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0023,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9901,0.0103,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0038,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0040,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.9459,0.2379,0.0077</t>
-  </si>
-  <si>
-    <t>0.0059,0.7002,0.8172,0.0021</t>
-  </si>
-  <si>
-    <t>0.0219,0.1413,0.9065,0.0148</t>
-  </si>
-  <si>
-    <t>0.0148,0.0655,0.9336,0.0291</t>
-  </si>
-  <si>
-    <t>0.9678,0.0102,0.0085,0.0027</t>
-  </si>
-  <si>
-    <t>0.8932,0.0483,0.0349,0.0057</t>
-  </si>
-  <si>
-    <t>0.9588,0.0056,0.0213,0.0038</t>
-  </si>
-  <si>
-    <t>0.9043,0.0308,0.0412,0.0032</t>
-  </si>
-  <si>
-    <t>0.3249,0.0009,0.0001,0.8209</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.0662,0.0001,0.0000,0.9825</t>
-  </si>
-  <si>
-    <t>0.0001,0.9814,0.4881,0.0004</t>
-  </si>
-  <si>
-    <t>0.9470,0.0739,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9706,0.0349,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9574,0.0012,0.0005,0.0233</t>
-  </si>
-  <si>
-    <t>0.9985,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.3678,0.9781</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9935,0.0050,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.8403,0.2369,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.9890,0.0075,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9799,0.0186,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.7181,0.3340,0.0105,0.0025</t>
-  </si>
-  <si>
-    <t>0.9337,0.0617,0.0097,0.0014</t>
-  </si>
-  <si>
-    <t>0.9280,0.0871,0.0059,0.0011</t>
-  </si>
-  <si>
-    <t>0.9986,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
     <t>0.9991,0.0007,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9624,0.0421,0.0035,0.0008</t>
-  </si>
-  <si>
-    <t>0.9807,0.0238,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9794,0.0308,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9409,0.0811,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0057,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9850,0.0173,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0024,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0065,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9973,0.0152</t>
-  </si>
-  <si>
-    <t>0.9967,0.0033,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0117,0.0068,0.9825,0.0040</t>
-  </si>
-  <si>
-    <t>0.0054,0.0102,0.9819,0.0109</t>
-  </si>
-  <si>
-    <t>0.0720,0.0031,0.9411,0.0026</t>
-  </si>
-  <si>
-    <t>0.0010,0.0159,0.9859,0.0205</t>
-  </si>
-  <si>
-    <t>0.0184,0.0008,0.9719,0.0064</t>
-  </si>
-  <si>
-    <t>0.0096,0.0010,0.9881,0.0028</t>
-  </si>
-  <si>
-    <t>0.0373,0.0046,0.9521,0.0094</t>
-  </si>
-  <si>
-    <t>0.3471,0.0104,0.6863,0.0061</t>
-  </si>
-  <si>
-    <t>0.3526,0.0089,0.6604,0.0112</t>
-  </si>
-  <si>
-    <t>0.5720,0.0234,0.4341,0.0092</t>
-  </si>
-  <si>
-    <t>0.7937,0.0409,0.1435,0.0115</t>
-  </si>
-  <si>
-    <t>0.6326,0.1332,0.1977,0.0136</t>
-  </si>
-  <si>
-    <t>0.7670,0.0606,0.1476,0.0056</t>
-  </si>
-  <si>
-    <t>0.8513,0.0623,0.0558,0.0107</t>
-  </si>
-  <si>
-    <t>0.8469,0.1604,0.0105,0.0040</t>
-  </si>
-  <si>
-    <t>0.9427,0.0919,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9908,0.0156,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0202,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9840,0.0236,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0073,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5927,0.3576,0.0551,0.0063</t>
-  </si>
-  <si>
-    <t>0.9605,0.0277,0.0069,0.0010</t>
-  </si>
-  <si>
-    <t>0.9278,0.0169,0.0221,0.0092</t>
-  </si>
-  <si>
-    <t>0.7411,0.1068,0.1085,0.0090</t>
-  </si>
-  <si>
-    <t>0.9812,0.0075,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.0110,0.0012,0.9748,0.0232</t>
-  </si>
-  <si>
-    <t>0.0636,0.0110,0.8517,0.0806</t>
-  </si>
-  <si>
-    <t>0.1314,0.0344,0.8315,0.0122</t>
-  </si>
-  <si>
-    <t>0.0285,0.0015,0.9669,0.0036</t>
-  </si>
-  <si>
-    <t>0.0830,0.0800,0.8188,0.0454</t>
-  </si>
-  <si>
-    <t>0.9977,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0041,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0515,0.0021,0.9215,0.0216</t>
-  </si>
-  <si>
-    <t>0.4634,0.5301,0.0252,0.0133</t>
-  </si>
-  <si>
-    <t>0.9946,0.0031,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.0014,0.9924,0.0019</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9973,0.0127</t>
-  </si>
-  <si>
-    <t>0.0784,0.0050,0.8991,0.0184</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9974,0.0059</t>
-  </si>
-  <si>
-    <t>0.0598,0.0038,0.9332,0.0077</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.0114,0.7578,0.5255</t>
-  </si>
-  <si>
-    <t>0.2168,0.0428,0.7394,0.0158</t>
-  </si>
-  <si>
-    <t>0.8783,0.0183,0.0475,0.0248</t>
-  </si>
-  <si>
-    <t>0.9460,0.0065,0.0097,0.0125</t>
-  </si>
-  <si>
-    <t>0.9291,0.0127,0.0202,0.0159</t>
-  </si>
-  <si>
-    <t>0.9972,0.0028,0.0001,0.0001</t>
+    <t>0.1301,0.0042,0.8567,0.0141</t>
+  </si>
+  <si>
+    <t>0.8812,0.0884,0.0127,0.0069</t>
+  </si>
+  <si>
+    <t>0.9910,0.0020,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.0072,0.0009,0.9860,0.0074</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9936,0.0359</t>
+  </si>
+  <si>
+    <t>0.1391,0.0219,0.8357,0.0167</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9983,0.0039</t>
+  </si>
+  <si>
+    <t>0.0484,0.0031,0.9302,0.0202</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9987,0.0011</t>
+  </si>
+  <si>
+    <t>0.0068,0.0631,0.6422,0.4461</t>
+  </si>
+  <si>
+    <t>0.1079,0.0347,0.8453,0.0302</t>
+  </si>
+  <si>
+    <t>0.8349,0.0319,0.0728,0.0274</t>
+  </si>
+  <si>
+    <t>0.8656,0.0386,0.0636,0.0075</t>
+  </si>
+  <si>
+    <t>0.9628,0.0339,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.9930,0.0073,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0034,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0026,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9985,0.0016,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0036,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0047,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0675,0.0073,0.9262,0.0060</t>
-  </si>
-  <si>
-    <t>0.0080,0.0052,0.9878,0.0025</t>
-  </si>
-  <si>
-    <t>0.0108,0.0138,0.9759,0.0127</t>
-  </si>
-  <si>
-    <t>0.3245,0.0685,0.5760,0.0121</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9937,0.0112</t>
-  </si>
-  <si>
-    <t>0.0538,0.0003,0.5367,0.2891</t>
-  </si>
-  <si>
-    <t>0.3427,0.0059,0.5931,0.0352</t>
-  </si>
-  <si>
-    <t>0.2453,0.0945,0.5947,0.0252</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0731,0.0013,0.0002,0.9731</t>
-  </si>
-  <si>
-    <t>0.8541,0.0005,0.0001,0.1779</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0215,0.0001,0.0000,0.9958</t>
-  </si>
-  <si>
-    <t>0.9920,0.0025,0.0006,0.0011</t>
+    <t>0.9985,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0550,0.1225,0.8659,0.0117</t>
+  </si>
+  <si>
+    <t>0.0019,0.0039,0.9950,0.0029</t>
+  </si>
+  <si>
+    <t>0.0142,0.0137,0.9779,0.0039</t>
+  </si>
+  <si>
+    <t>0.3425,0.0934,0.5074,0.0299</t>
+  </si>
+  <si>
+    <t>0.0054,0.0011,0.9848,0.0172</t>
+  </si>
+  <si>
+    <t>0.0417,0.0008,0.2285,0.7320</t>
+  </si>
+  <si>
+    <t>0.2179,0.0044,0.7796,0.0124</t>
+  </si>
+  <si>
+    <t>0.0533,0.5017,0.2920,0.1518</t>
+  </si>
+  <si>
+    <t>0.9941,0.0030,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.4402,0.0030,0.0005,0.6668</t>
+  </si>
+  <si>
+    <t>0.7728,0.0007,0.0002,0.2886</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.1017,0.0001,0.0000,0.9753</t>
+  </si>
+  <si>
+    <t>0.9827,0.0034,0.0011,0.0035</t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2110,10 +2119,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2390,10 +2399,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2530,10 +2539,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2575,7 +2584,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2950,10 +2959,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3048,10 +3057,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3076,10 +3085,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>360</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>361</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3524,10 +3533,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3622,10 +3631,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3958,10 +3967,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>356</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>416</v>
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>356</v>
+        <v>424</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4546,10 +4555,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4560,10 +4569,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>321</v>
+        <v>468</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>470</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4994,10 +5003,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5106,10 +5115,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>487</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>271</v>
+        <v>493</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5358,10 +5367,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5386,10 +5395,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D250" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D253" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
